--- a/data/trans_dic/P05A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P05A_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,99; 23,48</t>
+          <t>14,16; 23,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,0; 51,14</t>
+          <t>39,21; 50,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,01; 42,82</t>
+          <t>30,59; 42,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,51</t>
+          <t>1,76; 5,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,64; 22,1</t>
+          <t>12,61; 21,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,21; 51,48</t>
+          <t>39,05; 51,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,77; 54,62</t>
+          <t>42,42; 54,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,84</t>
+          <t>2,32; 5,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,5; 21,14</t>
+          <t>14,87; 21,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40,95; 49,41</t>
+          <t>40,97; 49,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,46; 46,85</t>
+          <t>38,17; 46,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,62</t>
+          <t>2,48; 5,08</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,58; 37,41</t>
+          <t>28,49; 37,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,21; 43,63</t>
+          <t>34,6; 43,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50,0; 58,87</t>
+          <t>49,89; 59,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,04; 19,66</t>
+          <t>11,1; 18,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,76; 40,48</t>
+          <t>31,3; 40,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,97; 46,72</t>
+          <t>37,6; 46,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,9; 56,26</t>
+          <t>46,98; 56,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,95; 16,46</t>
+          <t>10,76; 16,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,41; 37,68</t>
+          <t>31,46; 37,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,1; 43,6</t>
+          <t>36,83; 43,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49,97; 56,48</t>
+          <t>49,97; 56,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,71; 16,95</t>
+          <t>11,47; 16,41</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,25; 26,58</t>
+          <t>17,42; 26,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,9; 50,62</t>
+          <t>39,7; 51,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,98; 36,1</t>
+          <t>26,09; 36,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,4; 28,74</t>
+          <t>19,44; 28,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,85; 43,96</t>
+          <t>33,34; 43,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,13; 58,2</t>
+          <t>46,52; 57,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,74; 33,7</t>
+          <t>23,21; 33,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,26; 26,13</t>
+          <t>18,39; 25,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,97; 34,2</t>
+          <t>26,88; 33,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,16; 53,1</t>
+          <t>45,15; 52,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,35; 33,35</t>
+          <t>26,07; 33,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,82; 25,45</t>
+          <t>20,02; 25,88</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,92; 34,37</t>
+          <t>25,1; 34,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,85; 38,4</t>
+          <t>28,32; 38,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,17; 36,3</t>
+          <t>26,52; 36,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,62; 26,53</t>
+          <t>14,48; 24,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,62; 29,45</t>
+          <t>20,3; 29,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,08; 46,3</t>
+          <t>36,08; 45,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,57; 41,49</t>
+          <t>30,79; 41,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,27; 22,09</t>
+          <t>17,39; 25,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,84; 30,11</t>
+          <t>23,73; 30,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,36; 40,61</t>
+          <t>33,19; 40,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,42; 37,3</t>
+          <t>30,17; 37,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,99; 21,76</t>
+          <t>17,37; 23,84</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,88; 54,05</t>
+          <t>40,11; 54,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,28; 75,26</t>
+          <t>62,45; 75,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,85; 29,26</t>
+          <t>17,67; 28,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,88</t>
+          <t>3,33; 9,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,48; 51,47</t>
+          <t>37,65; 51,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,29; 68,7</t>
+          <t>55,22; 68,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,68; 29,97</t>
+          <t>18,68; 30,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,5</t>
+          <t>1,08; 3,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40,87; 50,88</t>
+          <t>40,56; 50,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60,87; 70,0</t>
+          <t>60,76; 70,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19,87; 27,69</t>
+          <t>19,97; 27,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,99</t>
+          <t>2,53; 5,81</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,43; 21,09</t>
+          <t>12,81; 21,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,33; 56,95</t>
+          <t>45,42; 57,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,62; 46,06</t>
+          <t>33,85; 46,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,19; 24,03</t>
+          <t>14,73; 23,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,46; 33,93</t>
+          <t>23,23; 34,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,58; 49,44</t>
+          <t>37,3; 49,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,41; 38,44</t>
+          <t>26,77; 38,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,96; 24,86</t>
+          <t>17,38; 25,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,19; 26,31</t>
+          <t>19,16; 26,22</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43,09; 51,67</t>
+          <t>42,49; 51,88</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31,52; 40,27</t>
+          <t>31,98; 40,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,29; 23,04</t>
+          <t>17,22; 23,08</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,12; 27,19</t>
+          <t>19,68; 27,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,0; 45,95</t>
+          <t>38,33; 46,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,84; 42,55</t>
+          <t>34,97; 43,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28,51; 37,53</t>
+          <t>28,73; 36,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,17; 36,61</t>
+          <t>29,43; 37,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,23; 44,16</t>
+          <t>36,51; 44,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,87; 44,41</t>
+          <t>36,79; 44,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,17; 75,32</t>
+          <t>32,02; 38,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,97; 31,2</t>
+          <t>25,49; 30,78</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38,32; 43,74</t>
+          <t>38,25; 43,61</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36,95; 42,42</t>
+          <t>37,06; 42,6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,8; 68,0</t>
+          <t>31,25; 36,51</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>35,88; 43,01</t>
+          <t>35,79; 42,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,84; 28,08</t>
+          <t>22,06; 28,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,59; 31,64</t>
+          <t>24,85; 31,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,05; 16,41</t>
+          <t>13,2; 18,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,14; 46,25</t>
+          <t>39,09; 46,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,03; 26,62</t>
+          <t>20,73; 26,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,54; 30,56</t>
+          <t>24,56; 30,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,0; 23,06</t>
+          <t>19,07; 24,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,57; 43,58</t>
+          <t>38,46; 43,6</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22,04; 26,54</t>
+          <t>22,28; 26,8</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25,48; 30,11</t>
+          <t>25,54; 30,06</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,94; 18,68</t>
+          <t>16,87; 20,62</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,05; 31,38</t>
+          <t>28,09; 31,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38,02; 41,34</t>
+          <t>37,95; 41,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34,35; 37,62</t>
+          <t>34,32; 37,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,13</t>
+          <t>17,07; 19,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,78; 36,09</t>
+          <t>32,88; 36,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,27; 41,63</t>
+          <t>38,26; 41,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,87; 38,24</t>
+          <t>34,91; 38,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,74; 38,91</t>
+          <t>19,33; 21,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30,91; 33,3</t>
+          <t>30,77; 33,17</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38,58; 41,1</t>
+          <t>38,48; 40,98</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35,17; 37,43</t>
+          <t>35,15; 37,43</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,58; 28,84</t>
+          <t>18,6; 20,44</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20175</t>
+          <t>23488</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>38194; 64098</t>
+          <t>38661; 64988</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>113659; 149039</t>
+          <t>114267; 148618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91108; 125775</t>
+          <t>89857; 123980</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4389; 20264</t>
+          <t>5599; 18977</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32976; 57657</t>
+          <t>32889; 56960</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>111108; 145889</t>
+          <t>110651; 147071</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>123482; 157700</t>
+          <t>122478; 157982</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6691; 16903</t>
+          <t>7333; 18750</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>77394; 112874</t>
+          <t>79391; 114585</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>235371; 283984</t>
+          <t>235519; 286595</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>223992; 272893</t>
+          <t>222301; 272351</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13493; 33772</t>
+          <t>15746; 32222</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75581</t>
+          <t>76550</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>68843</t>
+          <t>73053</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>144424</t>
+          <t>149604</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>140942; 184478</t>
+          <t>140483; 185279</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>172948; 220558</t>
+          <t>174901; 221521</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>251299; 295872</t>
+          <t>250715; 296757</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57211; 101941</t>
+          <t>58879; 98332</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>160054; 204013</t>
+          <t>157732; 202062</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>198873; 244702</t>
+          <t>196961; 243331</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>245347; 294277</t>
+          <t>245760; 294134</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56374; 84771</t>
+          <t>58805; 87842</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>313175; 375643</t>
+          <t>313621; 376420</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381873; 448745</t>
+          <t>379134; 445741</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512481; 579263</t>
+          <t>512522; 577705</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>121037; 175189</t>
+          <t>123588; 176793</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75131</t>
+          <t>75012</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>75185</t>
+          <t>77793</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>150316</t>
+          <t>152805</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55010; 84761</t>
+          <t>55553; 84848</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>128918; 163562</t>
+          <t>128278; 165827</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82759; 115002</t>
+          <t>83101; 116089</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61320; 90829</t>
+          <t>61417; 89458</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>113525; 147449</t>
+          <t>111816; 146599</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>160725; 198490</t>
+          <t>158626; 197513</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79849; 113335</t>
+          <t>78057; 112233</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63745; 91213</t>
+          <t>65539; 91968</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>176469; 223769</t>
+          <t>175881; 222239</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>299929; 352636</t>
+          <t>299845; 351114</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>172555; 218428</t>
+          <t>170748; 217197</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>131851; 169283</t>
+          <t>134601; 174039</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64682</t>
+          <t>70775</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>78372</t>
+          <t>88843</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>143054</t>
+          <t>159619</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89387; 123260</t>
+          <t>90029; 122644</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>103844; 143154</t>
+          <t>105569; 142699</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96491; 133821</t>
+          <t>97771; 134576</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48807; 82912</t>
+          <t>54030; 93201</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>76600; 109384</t>
+          <t>75420; 108658</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>139641; 179185</t>
+          <t>139604; 177348</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>122274; 160701</t>
+          <t>119244; 158972</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>48808; 104928</t>
+          <t>73266; 106701</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>174053; 219860</t>
+          <t>173245; 220651</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>253446; 308575</t>
+          <t>252176; 308884</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>229959; 282008</t>
+          <t>228085; 282254</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>102333; 171362</t>
+          <t>137955; 189421</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>12080</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>16723</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>81077; 109891</t>
+          <t>81552; 109992</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>132421; 160008</t>
+          <t>132788; 160999</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37711; 61798</t>
+          <t>37317; 60610</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4686; 14090</t>
+          <t>6858; 19886</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>79910; 106884</t>
+          <t>78193; 106646</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>121422; 150868</t>
+          <t>121262; 149682</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40835; 65505</t>
+          <t>40840; 66608</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1904; 11638</t>
+          <t>2484; 8836</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>167946; 209088</t>
+          <t>166701; 206846</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>263076; 302553</t>
+          <t>262618; 303113</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85414; 119024</t>
+          <t>85825; 118823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7796; 21842</t>
+          <t>10984; 25257</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52019</t>
+          <t>50814</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>53145</t>
+          <t>55086</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>105164</t>
+          <t>105899</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33659; 57101</t>
+          <t>34693; 58169</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>121460; 156040</t>
+          <t>124431; 157567</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>88474; 121202</t>
+          <t>89066; 121530</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40952; 64795</t>
+          <t>39874; 63176</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>65265; 94364</t>
+          <t>64622; 95235</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>105228; 138459</t>
+          <t>104447; 138679</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>74578; 104600</t>
+          <t>72848; 105578</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>43608; 63896</t>
+          <t>45839; 66868</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>105367; 144450</t>
+          <t>105182; 143936</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>238741; 286233</t>
+          <t>235394; 287401</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>168689; 215544</t>
+          <t>171157; 216802</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>91041; 121367</t>
+          <t>92008; 123349</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>203878</t>
+          <t>231614</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>437022</t>
+          <t>270967</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>640900</t>
+          <t>502580</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>123723; 167245</t>
+          <t>121052; 167965</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>251860; 304570</t>
+          <t>254076; 305532</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>228751; 279358</t>
+          <t>229603; 283113</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>177880; 234147</t>
+          <t>206141; 263471</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>186153; 233653</t>
+          <t>187830; 237671</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>251382; 306417</t>
+          <t>253297; 306445</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>254425; 306420</t>
+          <t>253845; 308405</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>298449; 639146</t>
+          <t>246992; 298126</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>325475; 391073</t>
+          <t>319468; 385772</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>519854; 593360</t>
+          <t>518869; 591658</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>497592; 571199</t>
+          <t>499063; 573639</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>497639; 1001261</t>
+          <t>465291; 543568</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>105342</t>
+          <t>126928</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>146601</t>
+          <t>178654</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>251943</t>
+          <t>305582</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>266887; 319913</t>
+          <t>266176; 319703</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>170193; 218796</t>
+          <t>171870; 222745</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>191456; 246306</t>
+          <t>193445; 242779</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>46908; 152406</t>
+          <t>105309; 148022</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>306645; 362405</t>
+          <t>306272; 362399</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>165029; 219285</t>
+          <t>170815; 219906</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>202726; 252509</t>
+          <t>202948; 255198</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>129185; 165504</t>
+          <t>158534; 201998</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>589087; 665619</t>
+          <t>587349; 665899</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>353225; 425480</t>
+          <t>357125; 429583</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>408937; 483201</t>
+          <t>409890; 482371</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>163650; 307630</t>
+          <t>274808; 336035</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>594599</t>
+          <t>654993</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>875086</t>
+          <t>761307</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1469685</t>
+          <t>1416300</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>919208; 1028197</t>
+          <t>920308; 1021510</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1300708; 1414412</t>
+          <t>1298317; 1417843</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1165437; 1276521</t>
+          <t>1164617; 1275558</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>466842; 661663</t>
+          <t>602590; 704913</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1107855; 1219558</t>
+          <t>1111094; 1220849</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1359477; 1478927</t>
+          <t>1359339; 1479418</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1235034; 1354433</t>
+          <t>1236745; 1356620</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>695495; 1443886</t>
+          <t>722211; 810247</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2057115; 2216172</t>
+          <t>2048095; 2207510</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2690560; 2866196</t>
+          <t>2683574; 2858180</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2438907; 2595963</t>
+          <t>2437893; 2595935</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1260212; 2067857</t>
+          <t>1351245; 1485075</t>
         </is>
       </c>
     </row>
